--- a/графики/отчеты для СН/дефицит/Дефицит ПОКОМ КИ (Донецк).xlsx
+++ b/графики/отчеты для СН/дефицит/Дефицит ПОКОМ КИ (Донецк).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\отчеты для СН\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\отчеты для СН\дефицит\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3537B750-6AC6-4423-8A28-8B1FDE3235FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF2714B-6F39-4A35-852D-938672456FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TDSheet!$A$8:$J$124</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -656,17 +648,17 @@
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -682,7 +674,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -710,7 +702,7 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -722,73 +714,73 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1222,75 +1214,75 @@
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
     </row>
     <row r="7" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="27" t="s">
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="J8" s="45" t="s">
+      <c r="J8" s="46" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26" t="s">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="26"/>
+      <c r="F9" s="40"/>
       <c r="G9" s="5" t="s">
         <v>126</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="46"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="11.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="30">
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44">
         <v>69951.896999999997</v>
       </c>
-      <c r="F10" s="30"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="7"/>
       <c r="H10" s="6">
         <v>11723.857</v>
@@ -1301,16 +1293,16 @@
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32">
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="27">
         <v>873</v>
       </c>
-      <c r="F11" s="32"/>
+      <c r="F11" s="27"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12">
@@ -1319,16 +1311,16 @@
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="37">
         <v>69078.896999999997</v>
       </c>
-      <c r="F12" s="34"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="14"/>
       <c r="H12" s="13">
         <v>11723.857</v>
@@ -1339,16 +1331,16 @@
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="34">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37">
         <v>5893.2839999999997</v>
       </c>
-      <c r="F13" s="34"/>
+      <c r="F13" s="37"/>
       <c r="G13" s="14"/>
       <c r="H13" s="13">
         <v>1837.3679999999999</v>
@@ -1359,16 +1351,16 @@
       <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="32">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="27">
         <v>407.74299999999999</v>
       </c>
-      <c r="F14" s="32"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="16">
         <v>158.5</v>
       </c>
@@ -1381,16 +1373,16 @@
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="32">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27">
         <v>440.142</v>
       </c>
-      <c r="F15" s="32"/>
+      <c r="F15" s="27"/>
       <c r="G15" s="16">
         <v>178.9</v>
       </c>
@@ -1403,16 +1395,16 @@
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:16" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37">
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="35">
         <v>1980.704</v>
       </c>
-      <c r="F16" s="37"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="16">
         <v>456.5</v>
       </c>
@@ -1425,16 +1417,16 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="32">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="27">
         <v>143.98599999999999</v>
       </c>
-      <c r="F17" s="32"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="16">
         <v>11.7</v>
       </c>
@@ -1447,16 +1439,16 @@
       <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="35">
         <v>1019.022</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="16">
         <v>317.2</v>
       </c>
@@ -1469,16 +1461,16 @@
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="32">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27">
         <v>433.74</v>
       </c>
-      <c r="F19" s="32"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="16">
         <v>304.39999999999998</v>
       </c>
@@ -1491,16 +1483,16 @@
       <c r="J19" s="9"/>
     </row>
     <row r="20" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="32">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="27">
         <v>547.65899999999999</v>
       </c>
-      <c r="F20" s="32"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="16">
         <v>174.7</v>
       </c>
@@ -1513,16 +1505,16 @@
       <c r="J20" s="9"/>
     </row>
     <row r="21" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="32">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27">
         <v>54.052999999999997</v>
       </c>
-      <c r="F21" s="32"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="16">
         <v>9.1</v>
       </c>
@@ -1535,16 +1527,16 @@
       <c r="J21" s="9"/>
     </row>
     <row r="22" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="32">
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="27">
         <v>103.374</v>
       </c>
-      <c r="F22" s="32"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="16">
         <v>22.2</v>
       </c>
@@ -1557,16 +1549,16 @@
       <c r="J22" s="9"/>
     </row>
     <row r="23" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="32">
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="27">
         <v>632.16600000000005</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="16">
         <v>84.8</v>
       </c>
@@ -1579,16 +1571,16 @@
       <c r="J23" s="9"/>
     </row>
     <row r="24" spans="1:10" ht="11.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="32">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="27">
         <v>7.7130000000000001</v>
       </c>
-      <c r="F24" s="32"/>
+      <c r="F24" s="27"/>
       <c r="G24" s="18">
         <v>26.4</v>
       </c>
@@ -1604,16 +1596,16 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="32">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="27">
         <v>3</v>
       </c>
-      <c r="F25" s="32"/>
+      <c r="F25" s="27"/>
       <c r="G25" s="16">
         <v>0</v>
       </c>
@@ -1624,16 +1616,16 @@
       <c r="J25" s="9"/>
     </row>
     <row r="26" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="32">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="27">
         <v>119.982</v>
       </c>
-      <c r="F26" s="32"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="16">
         <v>13</v>
       </c>
@@ -1646,16 +1638,16 @@
       <c r="J26" s="9"/>
     </row>
     <row r="27" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34">
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37">
         <v>8782</v>
       </c>
-      <c r="F27" s="34"/>
+      <c r="F27" s="37"/>
       <c r="G27" s="16"/>
       <c r="H27" s="13">
         <v>1591.451</v>
@@ -1666,16 +1658,16 @@
       <c r="J27" s="9"/>
     </row>
     <row r="28" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="32">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="27">
         <v>17</v>
       </c>
-      <c r="F28" s="32"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="16">
         <v>0.4</v>
       </c>
@@ -1688,16 +1680,16 @@
       <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="35">
         <v>1682</v>
       </c>
-      <c r="F29" s="37"/>
+      <c r="F29" s="35"/>
       <c r="G29" s="16">
         <v>231.75</v>
       </c>
@@ -1710,16 +1702,16 @@
       <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="35">
         <v>1857</v>
       </c>
-      <c r="F30" s="37"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="16">
         <v>258.75</v>
       </c>
@@ -1732,16 +1724,16 @@
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="11.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="35">
         <v>1829</v>
       </c>
-      <c r="F31" s="37"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="18">
         <v>1075.95</v>
       </c>
@@ -1757,16 +1749,16 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="21.75" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="32">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="27">
         <v>2</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="27"/>
       <c r="G32" s="18">
         <v>3.15</v>
       </c>
@@ -1782,16 +1774,16 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="32">
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="27">
         <v>277</v>
       </c>
-      <c r="F33" s="32"/>
+      <c r="F33" s="27"/>
       <c r="G33" s="16">
         <v>43.65</v>
       </c>
@@ -1804,16 +1796,16 @@
       <c r="J33" s="9"/>
     </row>
     <row r="34" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="32">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="27">
         <v>13</v>
       </c>
-      <c r="F34" s="32"/>
+      <c r="F34" s="27"/>
       <c r="G34" s="16">
         <v>1.6</v>
       </c>
@@ -1826,16 +1818,16 @@
       <c r="J34" s="9"/>
     </row>
     <row r="35" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A35" s="36" t="s">
+      <c r="A35" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="32">
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="27">
         <v>12</v>
       </c>
-      <c r="F35" s="32"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="16">
         <v>0</v>
       </c>
@@ -1846,16 +1838,16 @@
       <c r="J35" s="9"/>
     </row>
     <row r="36" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="32">
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="27">
         <v>103</v>
       </c>
-      <c r="F36" s="32"/>
+      <c r="F36" s="27"/>
       <c r="G36" s="16">
         <v>2.4</v>
       </c>
@@ -1868,16 +1860,16 @@
       <c r="J36" s="9"/>
     </row>
     <row r="37" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="32">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="27">
         <v>189</v>
       </c>
-      <c r="F37" s="32"/>
+      <c r="F37" s="27"/>
       <c r="G37" s="16">
         <v>28.86</v>
       </c>
@@ -1890,16 +1882,16 @@
       <c r="J37" s="9"/>
     </row>
     <row r="38" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="32">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="27">
         <v>379</v>
       </c>
-      <c r="F38" s="32"/>
+      <c r="F38" s="27"/>
       <c r="G38" s="16">
         <v>66.66</v>
       </c>
@@ -1912,16 +1904,16 @@
       <c r="J38" s="9"/>
     </row>
     <row r="39" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="32">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="27">
         <v>75</v>
       </c>
-      <c r="F39" s="32"/>
+      <c r="F39" s="27"/>
       <c r="G39" s="16">
         <v>2.4</v>
       </c>
@@ -1934,16 +1926,16 @@
       <c r="J39" s="9"/>
     </row>
     <row r="40" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="32">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="27">
         <v>40</v>
       </c>
-      <c r="F40" s="32"/>
+      <c r="F40" s="27"/>
       <c r="G40" s="16">
         <v>2.2000000000000002</v>
       </c>
@@ -1956,16 +1948,16 @@
       <c r="J40" s="9"/>
     </row>
     <row r="41" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="32">
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="27">
         <v>2</v>
       </c>
-      <c r="F41" s="32"/>
+      <c r="F41" s="27"/>
       <c r="G41" s="16">
         <v>1.7</v>
       </c>
@@ -1976,16 +1968,16 @@
       <c r="J41" s="9"/>
     </row>
     <row r="42" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A42" s="36" t="s">
+      <c r="A42" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="32">
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="27">
         <v>534</v>
       </c>
-      <c r="F42" s="32"/>
+      <c r="F42" s="27"/>
       <c r="G42" s="16">
         <v>38.36</v>
       </c>
@@ -1998,16 +1990,16 @@
       <c r="J42" s="9"/>
     </row>
     <row r="43" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="37">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="35">
         <v>1272</v>
       </c>
-      <c r="F43" s="37"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="16">
         <v>51.8</v>
       </c>
@@ -2020,16 +2012,16 @@
       <c r="J43" s="9"/>
     </row>
     <row r="44" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="32">
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="27">
         <v>492</v>
       </c>
-      <c r="F44" s="32"/>
+      <c r="F44" s="27"/>
       <c r="G44" s="16">
         <v>46.76</v>
       </c>
@@ -2042,16 +2034,16 @@
       <c r="J44" s="9"/>
     </row>
     <row r="45" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="32">
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="27">
         <v>4</v>
       </c>
-      <c r="F45" s="32"/>
+      <c r="F45" s="27"/>
       <c r="G45" s="16">
         <v>7.47</v>
       </c>
@@ -2062,16 +2054,16 @@
       <c r="J45" s="9"/>
     </row>
     <row r="46" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="32">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="27">
         <v>3</v>
       </c>
-      <c r="F46" s="32"/>
+      <c r="F46" s="27"/>
       <c r="G46" s="16">
         <v>7.47</v>
       </c>
@@ -2084,16 +2076,16 @@
       <c r="J46" s="9"/>
     </row>
     <row r="47" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="34">
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="37">
         <v>37907.612999999998</v>
       </c>
-      <c r="F47" s="34"/>
+      <c r="F47" s="37"/>
       <c r="G47" s="16"/>
       <c r="H47" s="13">
         <v>6413.4719999999998</v>
@@ -2104,16 +2096,16 @@
       <c r="J47" s="9"/>
     </row>
     <row r="48" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="37">
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="35">
         <v>2832.8440000000001</v>
       </c>
-      <c r="F48" s="37"/>
+      <c r="F48" s="35"/>
       <c r="G48" s="16">
         <v>532.85</v>
       </c>
@@ -2126,16 +2118,16 @@
       <c r="J48" s="9"/>
     </row>
     <row r="49" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37">
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="35">
         <v>2559.4989999999998</v>
       </c>
-      <c r="F49" s="37"/>
+      <c r="F49" s="35"/>
       <c r="G49" s="16">
         <v>712.5</v>
       </c>
@@ -2148,16 +2140,16 @@
       <c r="J49" s="9"/>
     </row>
     <row r="50" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="32">
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27">
         <v>75.585999999999999</v>
       </c>
-      <c r="F50" s="32"/>
+      <c r="F50" s="27"/>
       <c r="G50" s="16">
         <v>23.8</v>
       </c>
@@ -2170,16 +2162,16 @@
       <c r="J50" s="9"/>
     </row>
     <row r="51" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="32">
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="27">
         <v>11.113</v>
       </c>
-      <c r="F51" s="32"/>
+      <c r="F51" s="27"/>
       <c r="G51" s="16">
         <v>1.35</v>
       </c>
@@ -2192,16 +2184,16 @@
       <c r="J51" s="9"/>
     </row>
     <row r="52" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="37">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="35">
         <v>5491.0140000000001</v>
       </c>
-      <c r="F52" s="37"/>
+      <c r="F52" s="35"/>
       <c r="G52" s="16">
         <v>691.8</v>
       </c>
@@ -2214,16 +2206,16 @@
       <c r="J52" s="9"/>
     </row>
     <row r="53" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A53" s="36" t="s">
+      <c r="A53" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="32">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="27">
         <v>677.41099999999994</v>
       </c>
-      <c r="F53" s="32"/>
+      <c r="F53" s="27"/>
       <c r="G53" s="16">
         <v>68.150000000000006</v>
       </c>
@@ -2236,16 +2228,16 @@
       <c r="J53" s="9"/>
     </row>
     <row r="54" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A54" s="36" t="s">
+      <c r="A54" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="36"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="37">
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="35">
         <v>1499.7070000000001</v>
       </c>
-      <c r="F54" s="37"/>
+      <c r="F54" s="35"/>
       <c r="G54" s="16">
         <v>246.1</v>
       </c>
@@ -2258,16 +2250,16 @@
       <c r="J54" s="9"/>
     </row>
     <row r="55" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A55" s="36" t="s">
+      <c r="A55" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="32">
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="27">
         <v>943.71100000000001</v>
       </c>
-      <c r="F55" s="32"/>
+      <c r="F55" s="27"/>
       <c r="G55" s="16">
         <v>314.75</v>
       </c>
@@ -2280,16 +2272,16 @@
       <c r="J55" s="9"/>
     </row>
     <row r="56" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="32">
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="27">
         <v>-0.91800000000000004</v>
       </c>
-      <c r="F56" s="32"/>
+      <c r="F56" s="27"/>
       <c r="G56" s="16">
         <v>0</v>
       </c>
@@ -2300,16 +2292,16 @@
       <c r="J56" s="9"/>
     </row>
     <row r="57" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="36"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="32">
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="27">
         <v>34.438000000000002</v>
       </c>
-      <c r="F57" s="32"/>
+      <c r="F57" s="27"/>
       <c r="G57" s="16">
         <v>0</v>
       </c>
@@ -2320,16 +2312,16 @@
       <c r="J57" s="9"/>
     </row>
     <row r="58" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="32">
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="27">
         <v>821.62</v>
       </c>
-      <c r="F58" s="32"/>
+      <c r="F58" s="27"/>
       <c r="G58" s="16">
         <v>253.1</v>
       </c>
@@ -2342,16 +2334,16 @@
       <c r="J58" s="9"/>
     </row>
     <row r="59" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="37">
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="35">
         <v>2107.846</v>
       </c>
-      <c r="F59" s="37"/>
+      <c r="F59" s="35"/>
       <c r="G59" s="16">
         <v>618.70000000000005</v>
       </c>
@@ -2364,16 +2356,16 @@
       <c r="J59" s="9"/>
     </row>
     <row r="60" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A60" s="36" t="s">
+      <c r="A60" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="32">
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="27">
         <v>335.298</v>
       </c>
-      <c r="F60" s="32"/>
+      <c r="F60" s="27"/>
       <c r="G60" s="16">
         <v>2.7</v>
       </c>
@@ -2386,16 +2378,16 @@
       <c r="J60" s="9"/>
     </row>
     <row r="61" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="32">
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="27">
         <v>14.635999999999999</v>
       </c>
-      <c r="F61" s="32"/>
+      <c r="F61" s="27"/>
       <c r="G61" s="16">
         <v>0</v>
       </c>
@@ -2406,16 +2398,16 @@
       <c r="J61" s="9"/>
     </row>
     <row r="62" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="32">
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="27">
         <v>240.637</v>
       </c>
-      <c r="F62" s="32"/>
+      <c r="F62" s="27"/>
       <c r="G62" s="16">
         <v>15.9</v>
       </c>
@@ -2428,16 +2420,16 @@
       <c r="J62" s="9"/>
     </row>
     <row r="63" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="37">
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="35">
         <v>1738.6379999999999</v>
       </c>
-      <c r="F63" s="37"/>
+      <c r="F63" s="35"/>
       <c r="G63" s="16">
         <v>246.9</v>
       </c>
@@ -2450,16 +2442,16 @@
       <c r="J63" s="9"/>
     </row>
     <row r="64" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="32">
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="27">
         <v>203.333</v>
       </c>
-      <c r="F64" s="32"/>
+      <c r="F64" s="27"/>
       <c r="G64" s="16">
         <v>121.2</v>
       </c>
@@ -2472,16 +2464,16 @@
       <c r="J64" s="9"/>
     </row>
     <row r="65" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="32">
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="27">
         <v>159.57300000000001</v>
       </c>
-      <c r="F65" s="32"/>
+      <c r="F65" s="27"/>
       <c r="G65" s="16">
         <v>10.6</v>
       </c>
@@ -2494,16 +2486,16 @@
       <c r="J65" s="9"/>
     </row>
     <row r="66" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A66" s="36" t="s">
+      <c r="A66" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="32">
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="27">
         <v>287.01799999999997</v>
       </c>
-      <c r="F66" s="32"/>
+      <c r="F66" s="27"/>
       <c r="G66" s="16">
         <v>10.5</v>
       </c>
@@ -2516,16 +2508,16 @@
       <c r="J66" s="9"/>
     </row>
     <row r="67" spans="1:10" ht="21.75" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A67" s="36" t="s">
+      <c r="A67" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="32">
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="27">
         <v>-2.8029999999999999</v>
       </c>
-      <c r="F67" s="32"/>
+      <c r="F67" s="27"/>
       <c r="G67" s="18">
         <v>60.2</v>
       </c>
@@ -2541,16 +2533,16 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A68" s="36" t="s">
+      <c r="A68" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="32">
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="27">
         <v>139.84399999999999</v>
       </c>
-      <c r="F68" s="32"/>
+      <c r="F68" s="27"/>
       <c r="G68" s="16">
         <v>14</v>
       </c>
@@ -2563,16 +2555,16 @@
       <c r="J68" s="9"/>
     </row>
     <row r="69" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A69" s="36" t="s">
+      <c r="A69" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="32">
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="27">
         <v>27.337</v>
       </c>
-      <c r="F69" s="32"/>
+      <c r="F69" s="27"/>
       <c r="G69" s="16">
         <v>1.3</v>
       </c>
@@ -2585,16 +2577,16 @@
       <c r="J69" s="9"/>
     </row>
     <row r="70" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="37">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="35">
         <v>3856.4740000000002</v>
       </c>
-      <c r="F70" s="37"/>
+      <c r="F70" s="35"/>
       <c r="G70" s="16">
         <v>441.6</v>
       </c>
@@ -2607,16 +2599,16 @@
       <c r="J70" s="9"/>
     </row>
     <row r="71" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A71" s="36" t="s">
+      <c r="A71" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="37">
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="35">
         <v>2201.0709999999999</v>
       </c>
-      <c r="F71" s="37"/>
+      <c r="F71" s="35"/>
       <c r="G71" s="16">
         <v>277.5</v>
       </c>
@@ -2629,16 +2621,16 @@
       <c r="J71" s="9"/>
     </row>
     <row r="72" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A72" s="36" t="s">
+      <c r="A72" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="37">
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="35">
         <v>3066.473</v>
       </c>
-      <c r="F72" s="37"/>
+      <c r="F72" s="35"/>
       <c r="G72" s="16">
         <v>415</v>
       </c>
@@ -2651,16 +2643,16 @@
       <c r="J72" s="9"/>
     </row>
     <row r="73" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="37">
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="35">
         <v>4929.8980000000001</v>
       </c>
-      <c r="F73" s="37"/>
+      <c r="F73" s="35"/>
       <c r="G73" s="16">
         <v>670</v>
       </c>
@@ -2673,16 +2665,16 @@
       <c r="J73" s="9"/>
     </row>
     <row r="74" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A74" s="36" t="s">
+      <c r="A74" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="32">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="27">
         <v>13.433999999999999</v>
       </c>
-      <c r="F74" s="32"/>
+      <c r="F74" s="27"/>
       <c r="G74" s="16">
         <v>1.3</v>
       </c>
@@ -2695,16 +2687,16 @@
       <c r="J74" s="9"/>
     </row>
     <row r="75" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A75" s="36" t="s">
+      <c r="A75" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="32">
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="27">
         <v>285.32799999999997</v>
       </c>
-      <c r="F75" s="32"/>
+      <c r="F75" s="27"/>
       <c r="G75" s="16">
         <v>83</v>
       </c>
@@ -2717,16 +2709,16 @@
       <c r="J75" s="9"/>
     </row>
     <row r="76" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="32">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="27">
         <v>16.481999999999999</v>
       </c>
-      <c r="F76" s="32"/>
+      <c r="F76" s="27"/>
       <c r="G76" s="16">
         <v>0</v>
       </c>
@@ -2737,16 +2729,16 @@
       <c r="J76" s="9"/>
     </row>
     <row r="77" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A77" s="36" t="s">
+      <c r="A77" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="32">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="27">
         <v>39.731999999999999</v>
       </c>
-      <c r="F77" s="32"/>
+      <c r="F77" s="27"/>
       <c r="G77" s="16">
         <v>7.5</v>
       </c>
@@ -2759,16 +2751,16 @@
       <c r="J77" s="9"/>
     </row>
     <row r="78" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="32">
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="27">
         <v>133.49199999999999</v>
       </c>
-      <c r="F78" s="32"/>
+      <c r="F78" s="27"/>
       <c r="G78" s="16">
         <v>2.5</v>
       </c>
@@ -2781,16 +2773,16 @@
       <c r="J78" s="9"/>
     </row>
     <row r="79" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A79" s="36" t="s">
+      <c r="A79" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="32">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="27">
         <v>217.238</v>
       </c>
-      <c r="F79" s="32"/>
+      <c r="F79" s="27"/>
       <c r="G79" s="16">
         <v>33.799999999999997</v>
       </c>
@@ -2803,16 +2795,16 @@
       <c r="J79" s="9"/>
     </row>
     <row r="80" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A80" s="36" t="s">
+      <c r="A80" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="32">
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="27">
         <v>706.06799999999998</v>
       </c>
-      <c r="F80" s="32"/>
+      <c r="F80" s="27"/>
       <c r="G80" s="16">
         <v>115.24</v>
       </c>
@@ -2825,16 +2817,16 @@
       <c r="J80" s="9"/>
     </row>
     <row r="81" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="36"/>
-      <c r="E81" s="32">
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="27">
         <v>133.69800000000001</v>
       </c>
-      <c r="F81" s="32"/>
+      <c r="F81" s="27"/>
       <c r="G81" s="16">
         <v>12.3</v>
       </c>
@@ -2847,16 +2839,16 @@
       <c r="J81" s="9"/>
     </row>
     <row r="82" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A82" s="36" t="s">
+      <c r="A82" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="36"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="36"/>
-      <c r="E82" s="37">
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="35">
         <v>2110.8429999999998</v>
       </c>
-      <c r="F82" s="37"/>
+      <c r="F82" s="35"/>
       <c r="G82" s="16">
         <v>257.39999999999998</v>
       </c>
@@ -2869,16 +2861,16 @@
       <c r="J82" s="9"/>
     </row>
     <row r="83" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A83" s="35" t="s">
+      <c r="A83" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="35"/>
-      <c r="C83" s="35"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="34">
+      <c r="B83" s="36"/>
+      <c r="C83" s="36"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="37">
         <v>16496</v>
       </c>
-      <c r="F83" s="34"/>
+      <c r="F83" s="37"/>
       <c r="G83" s="16"/>
       <c r="H83" s="13">
         <v>1881.566</v>
@@ -2889,16 +2881,16 @@
       <c r="J83" s="9"/>
     </row>
     <row r="84" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A84" s="36" t="s">
+      <c r="A84" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="32">
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="27">
         <v>271</v>
       </c>
-      <c r="F84" s="32"/>
+      <c r="F84" s="27"/>
       <c r="G84" s="16">
         <v>7.14</v>
       </c>
@@ -2911,16 +2903,16 @@
       <c r="J84" s="9"/>
     </row>
     <row r="85" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="32">
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="27">
         <v>43</v>
       </c>
-      <c r="F85" s="32"/>
+      <c r="F85" s="27"/>
       <c r="G85" s="16">
         <v>1.8</v>
       </c>
@@ -2933,16 +2925,16 @@
       <c r="J85" s="9"/>
     </row>
     <row r="86" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A86" s="36" t="s">
+      <c r="A86" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="36"/>
-      <c r="C86" s="36"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="32">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="27">
         <v>193</v>
       </c>
-      <c r="F86" s="32"/>
+      <c r="F86" s="27"/>
       <c r="G86" s="16">
         <v>8.84</v>
       </c>
@@ -2955,16 +2947,16 @@
       <c r="J86" s="9"/>
     </row>
     <row r="87" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A87" s="36" t="s">
+      <c r="A87" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="36"/>
-      <c r="C87" s="36"/>
-      <c r="D87" s="36"/>
-      <c r="E87" s="37">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="35">
         <v>3915</v>
       </c>
-      <c r="F87" s="37"/>
+      <c r="F87" s="35"/>
       <c r="G87" s="16">
         <v>365.6</v>
       </c>
@@ -2977,16 +2969,16 @@
       <c r="J87" s="9"/>
     </row>
     <row r="88" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A88" s="36" t="s">
+      <c r="A88" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36"/>
-      <c r="D88" s="36"/>
-      <c r="E88" s="37">
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="35">
         <v>1097</v>
       </c>
-      <c r="F88" s="37"/>
+      <c r="F88" s="35"/>
       <c r="G88" s="16">
         <v>91.2</v>
       </c>
@@ -2999,16 +2991,16 @@
       <c r="J88" s="9"/>
     </row>
     <row r="89" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A89" s="36" t="s">
+      <c r="A89" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="36"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="32">
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="27">
         <v>916</v>
       </c>
-      <c r="F89" s="32"/>
+      <c r="F89" s="27"/>
       <c r="G89" s="16">
         <v>84.8</v>
       </c>
@@ -3021,16 +3013,16 @@
       <c r="J89" s="9"/>
     </row>
     <row r="90" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A90" s="36" t="s">
+      <c r="A90" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="36"/>
-      <c r="E90" s="32">
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="27">
         <v>378</v>
       </c>
-      <c r="F90" s="32"/>
+      <c r="F90" s="27"/>
       <c r="G90" s="16">
         <v>7.7</v>
       </c>
@@ -3043,16 +3035,16 @@
       <c r="J90" s="9"/>
     </row>
     <row r="91" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A91" s="36" t="s">
+      <c r="A91" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="36"/>
-      <c r="C91" s="36"/>
-      <c r="D91" s="36"/>
-      <c r="E91" s="32">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="27">
         <v>80</v>
       </c>
-      <c r="F91" s="32"/>
+      <c r="F91" s="27"/>
       <c r="G91" s="16">
         <v>9.1</v>
       </c>
@@ -3065,16 +3057,16 @@
       <c r="J91" s="9"/>
     </row>
     <row r="92" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A92" s="36" t="s">
+      <c r="A92" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="36"/>
-      <c r="C92" s="36"/>
-      <c r="D92" s="36"/>
-      <c r="E92" s="32">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="27">
         <v>170</v>
       </c>
-      <c r="F92" s="32"/>
+      <c r="F92" s="27"/>
       <c r="G92" s="16">
         <v>40.4</v>
       </c>
@@ -3087,16 +3079,16 @@
       <c r="J92" s="9"/>
     </row>
     <row r="93" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A93" s="36" t="s">
+      <c r="A93" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="36"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="36"/>
-      <c r="E93" s="32">
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="27">
         <v>602</v>
       </c>
-      <c r="F93" s="32"/>
+      <c r="F93" s="27"/>
       <c r="G93" s="16">
         <v>46.8</v>
       </c>
@@ -3109,16 +3101,16 @@
       <c r="J93" s="9"/>
     </row>
     <row r="94" spans="1:10" ht="21.75" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A94" s="36" t="s">
+      <c r="A94" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="36"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="36"/>
-      <c r="E94" s="37">
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="35">
         <v>1953</v>
       </c>
-      <c r="F94" s="37"/>
+      <c r="F94" s="35"/>
       <c r="G94" s="18">
         <v>877.8</v>
       </c>
@@ -3134,16 +3126,16 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A95" s="36" t="s">
+      <c r="A95" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="32">
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="26"/>
+      <c r="E95" s="27">
         <v>673</v>
       </c>
-      <c r="F95" s="32"/>
+      <c r="F95" s="27"/>
       <c r="G95" s="16">
         <v>29.2</v>
       </c>
@@ -3156,16 +3148,16 @@
       <c r="J95" s="9"/>
     </row>
     <row r="96" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A96" s="36" t="s">
+      <c r="A96" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="36"/>
-      <c r="C96" s="36"/>
-      <c r="D96" s="36"/>
-      <c r="E96" s="32">
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="27">
         <v>19</v>
       </c>
-      <c r="F96" s="32"/>
+      <c r="F96" s="27"/>
       <c r="G96" s="16">
         <v>0</v>
       </c>
@@ -3176,16 +3168,16 @@
       <c r="J96" s="9"/>
     </row>
     <row r="97" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A97" s="36" t="s">
+      <c r="A97" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="32">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="27">
         <v>284</v>
       </c>
-      <c r="F97" s="32"/>
+      <c r="F97" s="27"/>
       <c r="G97" s="16">
         <v>4.7</v>
       </c>
@@ -3198,16 +3190,16 @@
       <c r="J97" s="9"/>
     </row>
     <row r="98" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A98" s="36" t="s">
+      <c r="A98" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="36"/>
-      <c r="C98" s="36"/>
-      <c r="D98" s="36"/>
-      <c r="E98" s="32">
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="27">
         <v>265</v>
       </c>
-      <c r="F98" s="32"/>
+      <c r="F98" s="27"/>
       <c r="G98" s="16">
         <v>5.0999999999999996</v>
       </c>
@@ -3220,16 +3212,16 @@
       <c r="J98" s="9"/>
     </row>
     <row r="99" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A99" s="36" t="s">
+      <c r="A99" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="32">
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="27">
         <v>826</v>
       </c>
-      <c r="F99" s="32"/>
+      <c r="F99" s="27"/>
       <c r="G99" s="16">
         <v>31.6</v>
       </c>
@@ -3242,16 +3234,16 @@
       <c r="J99" s="9"/>
     </row>
     <row r="100" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A100" s="36" t="s">
+      <c r="A100" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="32">
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="27">
         <v>266</v>
       </c>
-      <c r="F100" s="32"/>
+      <c r="F100" s="27"/>
       <c r="G100" s="16">
         <v>36.4</v>
       </c>
@@ -3264,16 +3256,16 @@
       <c r="J100" s="9"/>
     </row>
     <row r="101" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A101" s="36" t="s">
+      <c r="A101" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="32">
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="27">
         <v>848</v>
       </c>
-      <c r="F101" s="32"/>
+      <c r="F101" s="27"/>
       <c r="G101" s="16">
         <v>177</v>
       </c>
@@ -3286,16 +3278,16 @@
       <c r="J101" s="9"/>
     </row>
     <row r="102" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A102" s="36" t="s">
+      <c r="A102" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="32">
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="27">
         <v>753</v>
       </c>
-      <c r="F102" s="32"/>
+      <c r="F102" s="27"/>
       <c r="G102" s="16">
         <v>103.2</v>
       </c>
@@ -3308,16 +3300,16 @@
       <c r="J102" s="9"/>
     </row>
     <row r="103" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A103" s="36" t="s">
+      <c r="A103" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="36"/>
-      <c r="C103" s="36"/>
-      <c r="D103" s="36"/>
-      <c r="E103" s="32">
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="27">
         <v>52</v>
       </c>
-      <c r="F103" s="32"/>
+      <c r="F103" s="27"/>
       <c r="G103" s="16">
         <v>1.4</v>
       </c>
@@ -3330,16 +3322,16 @@
       <c r="J103" s="9"/>
     </row>
     <row r="104" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A104" s="36" t="s">
+      <c r="A104" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="36"/>
-      <c r="C104" s="36"/>
-      <c r="D104" s="36"/>
-      <c r="E104" s="37">
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="35">
         <v>1368</v>
       </c>
-      <c r="F104" s="37"/>
+      <c r="F104" s="35"/>
       <c r="G104" s="16">
         <v>98.4</v>
       </c>
@@ -3352,16 +3344,16 @@
       <c r="J104" s="9"/>
     </row>
     <row r="105" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A105" s="36" t="s">
+      <c r="A105" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="36"/>
-      <c r="C105" s="36"/>
-      <c r="D105" s="36"/>
-      <c r="E105" s="32">
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="26"/>
+      <c r="E105" s="27">
         <v>225</v>
       </c>
-      <c r="F105" s="32"/>
+      <c r="F105" s="27"/>
       <c r="G105" s="16">
         <v>8.0500000000000007</v>
       </c>
@@ -3374,16 +3366,16 @@
       <c r="J105" s="9"/>
     </row>
     <row r="106" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A106" s="36" t="s">
+      <c r="A106" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="32">
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="26"/>
+      <c r="E106" s="27">
         <v>87</v>
       </c>
-      <c r="F106" s="32"/>
+      <c r="F106" s="27"/>
       <c r="G106" s="16">
         <v>14</v>
       </c>
@@ -3396,16 +3388,16 @@
       <c r="J106" s="9"/>
     </row>
     <row r="107" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A107" s="36" t="s">
+      <c r="A107" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="36"/>
-      <c r="C107" s="36"/>
-      <c r="D107" s="36"/>
-      <c r="E107" s="32">
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="26"/>
+      <c r="E107" s="27">
         <v>52</v>
       </c>
-      <c r="F107" s="32"/>
+      <c r="F107" s="27"/>
       <c r="G107" s="16">
         <v>0</v>
       </c>
@@ -3416,16 +3408,16 @@
       <c r="J107" s="9"/>
     </row>
     <row r="108" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A108" s="36" t="s">
+      <c r="A108" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="36"/>
-      <c r="C108" s="36"/>
-      <c r="D108" s="36"/>
-      <c r="E108" s="32">
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="27">
         <v>111</v>
       </c>
-      <c r="F108" s="32"/>
+      <c r="F108" s="27"/>
       <c r="G108" s="16">
         <v>11.1</v>
       </c>
@@ -3438,16 +3430,16 @@
       <c r="J108" s="9"/>
     </row>
     <row r="109" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A109" s="36" t="s">
+      <c r="A109" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="36"/>
-      <c r="C109" s="36"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="32">
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="27">
         <v>43</v>
       </c>
-      <c r="F109" s="32"/>
+      <c r="F109" s="27"/>
       <c r="G109" s="16">
         <v>0.49</v>
       </c>
@@ -3460,16 +3452,16 @@
       <c r="J109" s="9"/>
     </row>
     <row r="110" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A110" s="36" t="s">
+      <c r="A110" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="36"/>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="32">
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="26"/>
+      <c r="E110" s="27">
         <v>21</v>
       </c>
-      <c r="F110" s="32"/>
+      <c r="F110" s="27"/>
       <c r="G110" s="16">
         <v>0.7</v>
       </c>
@@ -3482,16 +3474,16 @@
       <c r="J110" s="9"/>
     </row>
     <row r="111" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A111" s="36" t="s">
+      <c r="A111" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="32">
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="27">
         <v>85</v>
       </c>
-      <c r="F111" s="32"/>
+      <c r="F111" s="27"/>
       <c r="G111" s="16">
         <v>0.42</v>
       </c>
@@ -3504,16 +3496,16 @@
       <c r="J111" s="9"/>
     </row>
     <row r="112" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A112" s="36" t="s">
+      <c r="A112" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="36"/>
-      <c r="C112" s="36"/>
-      <c r="D112" s="36"/>
-      <c r="E112" s="32">
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="27">
         <v>51</v>
       </c>
-      <c r="F112" s="32"/>
+      <c r="F112" s="27"/>
       <c r="G112" s="16">
         <v>0.3</v>
       </c>
@@ -3526,16 +3518,16 @@
       <c r="J112" s="9"/>
     </row>
     <row r="113" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A113" s="36" t="s">
+      <c r="A113" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="36"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="32">
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="26"/>
+      <c r="E113" s="27">
         <v>150</v>
       </c>
-      <c r="F113" s="32"/>
+      <c r="F113" s="27"/>
       <c r="G113" s="16">
         <v>6.64</v>
       </c>
@@ -3548,16 +3540,16 @@
       <c r="J113" s="9"/>
     </row>
     <row r="114" spans="1:10" ht="21.75" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A114" s="36" t="s">
+      <c r="A114" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="36"/>
-      <c r="C114" s="36"/>
-      <c r="D114" s="36"/>
-      <c r="E114" s="32">
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="27">
         <v>19</v>
       </c>
-      <c r="F114" s="32"/>
+      <c r="F114" s="27"/>
       <c r="G114" s="18">
         <v>13.44</v>
       </c>
@@ -3571,16 +3563,16 @@
       </c>
     </row>
     <row r="115" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A115" s="36" t="s">
+      <c r="A115" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="36"/>
-      <c r="C115" s="36"/>
-      <c r="D115" s="36"/>
-      <c r="E115" s="32">
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="27">
         <v>152</v>
       </c>
-      <c r="F115" s="32"/>
+      <c r="F115" s="27"/>
       <c r="G115" s="16">
         <v>1.25</v>
       </c>
@@ -3593,16 +3585,16 @@
       <c r="J115" s="9"/>
     </row>
     <row r="116" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A116" s="36" t="s">
+      <c r="A116" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="32">
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="26"/>
+      <c r="E116" s="27">
         <v>82</v>
       </c>
-      <c r="F116" s="32"/>
+      <c r="F116" s="27"/>
       <c r="G116" s="16">
         <v>0</v>
       </c>
@@ -3613,16 +3605,16 @@
       <c r="J116" s="9"/>
     </row>
     <row r="117" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A117" s="36" t="s">
+      <c r="A117" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="32">
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="27">
         <v>153</v>
       </c>
-      <c r="F117" s="32"/>
+      <c r="F117" s="27"/>
       <c r="G117" s="16">
         <v>1.25</v>
       </c>
@@ -3635,16 +3627,16 @@
       <c r="J117" s="9"/>
     </row>
     <row r="118" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A118" s="36" t="s">
+      <c r="A118" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="36"/>
-      <c r="C118" s="36"/>
-      <c r="D118" s="36"/>
-      <c r="E118" s="32">
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="26"/>
+      <c r="E118" s="27">
         <v>35</v>
       </c>
-      <c r="F118" s="32"/>
+      <c r="F118" s="27"/>
       <c r="G118" s="16">
         <v>2.7</v>
       </c>
@@ -3657,16 +3649,16 @@
       <c r="J118" s="9"/>
     </row>
     <row r="119" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A119" s="36" t="s">
+      <c r="A119" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="36"/>
-      <c r="C119" s="36"/>
-      <c r="D119" s="36"/>
-      <c r="E119" s="32">
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="26"/>
+      <c r="E119" s="27">
         <v>47</v>
       </c>
-      <c r="F119" s="32"/>
+      <c r="F119" s="27"/>
       <c r="G119" s="16">
         <v>2.1</v>
       </c>
@@ -3679,16 +3671,16 @@
       <c r="J119" s="9"/>
     </row>
     <row r="120" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A120" s="36" t="s">
+      <c r="A120" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="36"/>
-      <c r="C120" s="36"/>
-      <c r="D120" s="36"/>
-      <c r="E120" s="32">
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="26"/>
+      <c r="E120" s="27">
         <v>7</v>
       </c>
-      <c r="F120" s="32"/>
+      <c r="F120" s="27"/>
       <c r="G120" s="16">
         <v>0</v>
       </c>
@@ -3699,16 +3691,16 @@
       <c r="J120" s="9"/>
     </row>
     <row r="121" spans="1:10" ht="11.25" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A121" s="36" t="s">
+      <c r="A121" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="32">
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="26"/>
+      <c r="E121" s="27">
         <v>98</v>
       </c>
-      <c r="F121" s="32"/>
+      <c r="F121" s="27"/>
       <c r="G121" s="16">
         <v>0.6</v>
       </c>
@@ -3721,16 +3713,16 @@
       <c r="J121" s="9"/>
     </row>
     <row r="122" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A122" s="36" t="s">
+      <c r="A122" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="36"/>
-      <c r="C122" s="36"/>
-      <c r="D122" s="36"/>
-      <c r="E122" s="32">
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="26"/>
+      <c r="E122" s="27">
         <v>79</v>
       </c>
-      <c r="F122" s="32"/>
+      <c r="F122" s="27"/>
       <c r="G122" s="16">
         <v>2.9</v>
       </c>
@@ -3743,16 +3735,16 @@
       <c r="J122" s="9"/>
     </row>
     <row r="123" spans="1:10" ht="21.75" hidden="1" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A123" s="42" t="s">
+      <c r="A123" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="43"/>
-      <c r="C123" s="43"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="40">
+      <c r="B123" s="33"/>
+      <c r="C123" s="33"/>
+      <c r="D123" s="34"/>
+      <c r="E123" s="30">
         <v>27</v>
       </c>
-      <c r="F123" s="41"/>
+      <c r="F123" s="31"/>
       <c r="G123" s="16">
         <v>0</v>
       </c>
@@ -3763,16 +3755,16 @@
       <c r="J123" s="9"/>
     </row>
     <row r="124" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="38" t="s">
+      <c r="A124" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="38"/>
-      <c r="C124" s="38"/>
-      <c r="D124" s="38"/>
-      <c r="E124" s="39">
+      <c r="B124" s="28"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="28"/>
+      <c r="E124" s="29">
         <v>69951.896999999997</v>
       </c>
-      <c r="F124" s="39"/>
+      <c r="F124" s="29"/>
       <c r="G124" s="23"/>
       <c r="H124" s="22">
         <v>11723.857</v>
@@ -3800,6 +3792,226 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="237">
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="E119:F119"/>
     <mergeCell ref="A120:D120"/>
     <mergeCell ref="E120:F120"/>
     <mergeCell ref="A115:D115"/>
@@ -3817,226 +4029,6 @@
     <mergeCell ref="E122:F122"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="E117:F117"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="E119:F119"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="A108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="A109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="A95:D95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="J8:J9"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4049,103 +4041,103 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="92.33203125" customWidth="1"/>
+    <col min="1" max="1" width="90" customWidth="1"/>
     <col min="2" max="2" width="11.1640625" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="101.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="97.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="25">
         <v>20.061</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="25" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="25">
         <v>261</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="25">
         <v>1.7999999999999998</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="25">
         <v>58.391000000000005</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="25">
         <v>193.89999999999998</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="25">
         <v>13.44</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="25" t="s">
         <v>137</v>
       </c>
     </row>
